--- a/Methodology/RNN/03-PWM-Y/Ts-03/Resumo_Estatisticas.xlsx
+++ b/Methodology/RNN/03-PWM-Y/Ts-03/Resumo_Estatisticas.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Todos_Modelos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Top_10_Modelos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Top_Modelos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Melhor_Modelo" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -473,7 +474,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.09124347571952494</v>
+        <v>-0.09124347571952487</v>
       </c>
       <c r="D2" t="n">
         <v>1.061807203375093</v>
@@ -482,7 +483,7 @@
         <v>0.09144180707312677</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08897516603786494</v>
+        <v>0.08897516603786493</v>
       </c>
     </row>
     <row r="3">
@@ -497,10 +498,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.4924098154901198</v>
+        <v>-0.4924098154901195</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5861865811649</v>
+        <v>1.586186581164899</v>
       </c>
       <c r="E3" t="n">
         <v>0.1606998146768676</v>
@@ -521,7 +522,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.4867564788875561</v>
+        <v>-0.486756478887556</v>
       </c>
       <c r="D4" t="n">
         <v>2.637002483024693</v>
@@ -569,7 +570,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.5554560099585819</v>
+        <v>-0.555456009958582</v>
       </c>
       <c r="D6" t="n">
         <v>1.624555021717927</v>
@@ -593,7 +594,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.8637361323471855</v>
+        <v>-0.8637361323471857</v>
       </c>
       <c r="D7" t="n">
         <v>3.28551531972441</v>
@@ -602,7 +603,7 @@
         <v>0.143148446313067</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2523513952396327</v>
+        <v>0.2523513952396326</v>
       </c>
     </row>
   </sheetData>
@@ -798,4 +799,218 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Best_Model</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Neurons</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Best_R2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Train_1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>model_4_1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>[16, 8, 4]</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9601504283070431</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Train_2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>model_16_1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>[32, 16]</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9871002950872633</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Val</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>model_128_4</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>[128]</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9927839362031228</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Test_1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>model_64_4</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>[264, 128, 64]</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9557423587730892</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Test_2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>model_16_3</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>[32, 16]</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9845166662313544</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Test_3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>model_64_2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>[64]</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9740811328468685</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>